--- a/supplementary-materials/tables/Table_S04.xlsx
+++ b/supplementary-materials/tables/Table_S04.xlsx
@@ -72,7 +72,7 @@
     <t>Is recording effort alone sufficient?</t>
   </si>
   <si>
-    <t>Standardised log recorded minutes</t>
+    <t/>
   </si>
   <si>
     <t>None</t>
